--- a/accountant-skill/data/Jan2026/payroll_journal.xlsx
+++ b/accountant-skill/data/Jan2026/payroll_journal.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Payroll Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>750000</v>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>960000</v>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>600000</v>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>360000</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>85000</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5110</v>
+        <v>62000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>120000</v>
